--- a/work_agents/Hunter - Mechnical Engineer/deliverables/4-CAL-0001.xlsx
+++ b/work_agents/Hunter - Mechnical Engineer/deliverables/4-CAL-0001.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Sarnia, Ontario, Canada</t>
+          <t>Sarnia, Canada</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>Generated by Mechanical Engineer Agent (Hunter)  |  2026-04-02T19:04:37  |  A Star Chemical</t>
+          <t>Generated by Mechanical Engineer Agent (Hunter)  |  2026-04-28T04:09:45  |  A Star Chemical</t>
         </is>
       </c>
     </row>
